--- a/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATT_MSM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ATT_MSM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,13 +480,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.011</v>
+        <v>-0.019</v>
       </c>
       <c r="D2" t="n">
         <v>-0.002</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.043</v>
+        <v>-0.037</v>
       </c>
       <c r="D3" t="n">
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03999999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.044</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.042</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -552,22 +552,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.094</v>
+        <v>0.045</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.027</v>
+        <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.025</v>
+        <v>0.094</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.043</v>
+        <v>-0.024</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.042</v>
+        <v>0.022</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.02</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>-0.001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.081</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.078</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.038</v>
+        <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.037</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.008</v>
+        <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.045</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.008</v>
+        <v>0.001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.037</v>
+        <v>0.006</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.005</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.01</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.028</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
+        <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.004</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.075</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.074</v>
+        <v>0.006</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>0.077</v>
       </c>
       <c r="D20" t="n">
         <v>-0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.018</v>
+        <v>0.076</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.109</v>
+        <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.106</v>
+        <v>0.019</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.19</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="E22" t="n">
-        <v>0.184</v>
+        <v>0.11</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.146</v>
+        <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="E23" t="n">
-        <v>0.143</v>
+        <v>0.191</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.051</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="E24" t="n">
-        <v>0.045</v>
+        <v>0.14</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.118</v>
+        <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.003</v>
+        <v>0.006</v>
       </c>
       <c r="E25" t="n">
-        <v>0.115</v>
+        <v>0.048</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.218</v>
+        <v>-0.128</v>
       </c>
       <c r="D26" t="n">
         <v>-0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.216</v>
+        <v>0.126</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.254</v>
+        <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.252</v>
+        <v>0.225</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.328</v>
+        <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="E28" t="n">
-        <v>0.327</v>
+        <v>0.384</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.436</v>
+        <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.428</v>
+        <v>0.396</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.06</v>
+        <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="E30" t="n">
-        <v>0.055</v>
+        <v>0.104</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.108</v>
+        <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.105</v>
+        <v>0.041</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.046</v>
+        <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="E32" t="n">
-        <v>0.045</v>
+        <v>0.059</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,45 +1317,18 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.068</v>
+        <v>0.022</v>
       </c>
       <c r="D33" t="n">
-        <v>0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E33" t="n">
-        <v>0.06200000000000001</v>
+        <v>0.018</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>region_North_America</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1412,16 +1385,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9000</v>
+        <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>541.114156846371</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0570484345693796</v>
+        <v>0.07201588164977409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2255693013305237</v>
+        <v>0.2496221955703657</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1444,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.441081701214957</v>
+        <v>1.415563718989383</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3574563098300351</v>
+        <v>0.3653792945421858</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7404802079014974</v>
+        <v>0.699433460990047</v>
       </c>
       <c r="E2" t="n">
-        <v>2.141683194528417</v>
+        <v>2.13169397698872</v>
       </c>
       <c r="F2" t="n">
-        <v>5.542424782173383e-05</v>
+        <v>0.0001069620034727781</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0140834678634234</v>
+        <v>0.01406648442462934</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0703902839533536</v>
+        <v>0.06948450970190394</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1238789535466973</v>
+        <v>-0.1221206520745263</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1520458892735441</v>
+        <v>0.150253620923785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8414204607733662</v>
+        <v>0.8395723070577604</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2017325771393508</v>
+        <v>0.1934376197861498</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1581404262436466</v>
+        <v>0.1561342593458452</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1082169627980094</v>
+        <v>-0.1125799052845432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.511682117076711</v>
+        <v>0.4994551448568427</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2020776105339761</v>
+        <v>0.2153756879251694</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08057006548401358</v>
+        <v>0.08228016691387022</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1249577682706334</v>
+        <v>0.1200746414081911</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1643426599149298</v>
+        <v>-0.1530618057027462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.325482790882957</v>
+        <v>0.3176221395304866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5190708243618176</v>
+        <v>0.4931913324621541</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2686624527710395</v>
+        <v>0.2682770111457028</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1323997932287733</v>
+        <v>0.130013240084899</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009163626482093679</v>
+        <v>0.01345574306594155</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5281612790599853</v>
+        <v>0.523098279225464</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04244039026816215</v>
+        <v>0.039069024183887</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05964226148582513</v>
+        <v>0.05866897476675003</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1415747831365014</v>
+        <v>0.138655478374334</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2178392145807862</v>
+        <v>-0.2130907691061169</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3371237375524365</v>
+        <v>0.330428718639617</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6735525056774656</v>
+        <v>0.6722020875369368</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0726365032279296</v>
+        <v>0.06280541537249595</v>
       </c>
       <c r="C8" t="n">
-        <v>0.149986825257263</v>
+        <v>0.1473120129983398</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2213322724318085</v>
+        <v>-0.2259208245943463</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3666052788876676</v>
+        <v>0.3515316553393382</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6281829879993032</v>
+        <v>0.6698580785094372</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1359892833809661</v>
+        <v>0.1390231384900846</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1249924798472538</v>
+        <v>0.120288228326492</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1089914754579998</v>
+        <v>-0.09673745679397036</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3809700422199319</v>
+        <v>0.3747837337741395</v>
       </c>
       <c r="F9" t="n">
-        <v>0.276604059935792</v>
+        <v>0.2477833667498957</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0412732047082739</v>
+        <v>0.02793986317350432</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1997597768127275</v>
+        <v>0.1999310656891016</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3502487634044314</v>
+        <v>-0.3639178249678465</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4327951728209792</v>
+        <v>0.4197975513148551</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8363111764796474</v>
+        <v>0.8888595085924254</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.08056505138514999</v>
+        <v>-0.07356614672567929</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2075907612650705</v>
+        <v>0.2061356399317544</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4874354669879406</v>
+        <v>-0.4775845769220345</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3263053642176406</v>
+        <v>0.3304522834706759</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6979453224064476</v>
+        <v>0.7211799737560187</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03339503869688849</v>
+        <v>0.03199774539716499</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2006439503274073</v>
+        <v>0.2061594449032441</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3598598776606735</v>
+        <v>-0.372067341685963</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4266499550544505</v>
+        <v>0.436062832480293</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8678112481037801</v>
+        <v>0.8766567670029284</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.005273936673435934</v>
+        <v>-0.006374277414136445</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1991086881849464</v>
+        <v>0.1965463686430545</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3955197945249467</v>
+        <v>-0.3915980812466558</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3849719211780748</v>
+        <v>0.3788495264183829</v>
       </c>
       <c r="F13" t="n">
-        <v>0.978868322210751</v>
+        <v>0.9741280078152985</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2421235205677746</v>
+        <v>-0.2378369521738852</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2108978279133912</v>
+        <v>0.2077401681853178</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6554756676957474</v>
+        <v>-0.6450001999594017</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1712286265601982</v>
+        <v>0.1693262956116314</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2509434818139851</v>
+        <v>0.2522600895661904</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.09228376646482196</v>
+        <v>-0.08511172439276481</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2190152094588149</v>
+        <v>0.2148668528732516</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5215456890705953</v>
+        <v>-0.5062430174958046</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3369781561409514</v>
+        <v>0.336019568710275</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6734938306617968</v>
+        <v>0.6920210823806994</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09868546647529974</v>
+        <v>0.09645326976338156</v>
       </c>
       <c r="C16" t="n">
-        <v>0.211463563208122</v>
+        <v>0.1999648883531895</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3157755014551286</v>
+        <v>-0.2954707095814427</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5131464344057282</v>
+        <v>0.4883772491082059</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6407300225930354</v>
+        <v>0.6295566025541415</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2637656510011511</v>
+        <v>-0.2658960001519028</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1968952506290443</v>
+        <v>0.1973633420962449</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6496732509610653</v>
+        <v>-0.6527210425290008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1221419489587631</v>
+        <v>0.1209290422251952</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1803675382069522</v>
+        <v>0.1779026046618571</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1368025458238696</v>
+        <v>0.1410581106617721</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1869365104736891</v>
+        <v>0.1862982201656765</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2295862821001556</v>
+        <v>-0.2240796912468675</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5031913737478948</v>
+        <v>0.5061959125704116</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4642827874229098</v>
+        <v>0.4489522418144455</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08448383857187276</v>
+        <v>-0.08344985283767306</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2107739350328812</v>
+        <v>0.2041354907480703</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4975931601161051</v>
+        <v>-0.4835480626703003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3286254829723596</v>
+        <v>0.3166483569949541</v>
       </c>
       <c r="F19" t="n">
-        <v>0.688547657668498</v>
+        <v>0.6826890852425085</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2657012916703951</v>
+        <v>-0.2678101521998021</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1925442743535581</v>
+        <v>0.1911082668602465</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6430811348327683</v>
+        <v>-0.6423754723937547</v>
       </c>
       <c r="E20" t="n">
-        <v>0.111678551491978</v>
+        <v>0.1067551679941506</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1676023276052617</v>
+        <v>0.1611085253078226</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2488073428506843</v>
+        <v>-0.2357850011436257</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1850800472649361</v>
+        <v>0.1852596407770944</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6115575697469301</v>
+        <v>-0.5988872248555588</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1139428840455614</v>
+        <v>0.1273172225683073</v>
       </c>
       <c r="F21" t="n">
-        <v>0.178843998791632</v>
+        <v>0.203114829079299</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06035477188473657</v>
+        <v>0.05887556586940961</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2003418636048243</v>
+        <v>0.1964795852898691</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3323080653763548</v>
+        <v>-0.3262173449960996</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4530176091458279</v>
+        <v>0.4439684767349188</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7632170696884718</v>
+        <v>0.7644423623312731</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1508512955560801</v>
+        <v>-0.1370978385961138</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2032773180572167</v>
+        <v>0.201594027127635</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5492675178221185</v>
+        <v>-0.532214871264669</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2475649267099582</v>
+        <v>0.2580191940724414</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4580291405945576</v>
+        <v>0.4964608030112682</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2037,23 +2010,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds[T.True]</t>
+          <t>performance_rating_Far_Exceeds[T.True]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.07574587252365932</v>
+        <v>0.1314300700432246</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06382768757980167</v>
+        <v>0.1025093436987393</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2008458413965451</v>
+        <v>-0.06948455168514248</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04935409634922648</v>
+        <v>0.3323446917715916</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2353363579506302</v>
+        <v>0.1997978500285618</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2062,23 +2035,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below[T.True]</t>
+          <t>performance_rating_Meets[T.True]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.05002505336534468</v>
+        <v>0.03463267714177365</v>
       </c>
       <c r="C25" t="n">
-        <v>0.04240067866181323</v>
+        <v>0.08275182901981309</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1331288564625546</v>
+        <v>-0.1275579273918765</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03307874973186523</v>
+        <v>0.1968232816754238</v>
       </c>
       <c r="F25" t="n">
-        <v>0.238072895317038</v>
+        <v>0.6755724289525702</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2087,23 +2060,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds[T.True]</t>
+          <t>region_Europe[T.True]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.05206493115741884</v>
+        <v>-0.1488260434975333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.07242481959477659</v>
+        <v>0.1041192044224461</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.08988510683515408</v>
+        <v>-0.3528959342644912</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1940149691499918</v>
+        <v>0.05524384726942458</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4722133557191446</v>
+        <v>0.1528946709271375</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2112,23 +2085,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Meets[T.True]</t>
+          <t>region_Latin_America[T.True]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04576047837771477</v>
+        <v>-0.03169527812066084</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0357607344342016</v>
+        <v>0.1100545842581242</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1158502299294513</v>
+        <v>-0.247398299600113</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02432927317402171</v>
+        <v>0.1840077433587913</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2006755912300271</v>
+        <v>0.7733498139601129</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2137,23 +2110,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Europe[T.True]</t>
+          <t>region_Middle_East_and_Africa[T.True]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1479233384529145</v>
+        <v>0.1415579970155404</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1080063382981191</v>
+        <v>0.1155062953631743</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3596118716192771</v>
+        <v>-0.08483018188392713</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06376519471344805</v>
+        <v>0.3679461759150079</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1708179952796579</v>
+        <v>0.2203704862681708</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2162,23 +2135,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Latin_America[T.True]</t>
+          <t>region_North_America[T.True]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02982664502419461</v>
+        <v>-0.02793447775400478</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1167056956216295</v>
+        <v>0.1096742534746417</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2585656052332822</v>
+        <v>-0.2428920645956194</v>
       </c>
       <c r="E29" t="n">
-        <v>0.198912315184893</v>
+        <v>0.1870231090876098</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7982817582485443</v>
+        <v>0.7989516794020014</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2187,23 +2160,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa[T.True]</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1486365527051748</v>
+        <v>0.2582177129441011</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1192949155393462</v>
+        <v>0.0379034316634053</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.08517718529069143</v>
+        <v>0.1839283519933516</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3824502907010411</v>
+        <v>0.3325070738948506</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2127795122694094</v>
+        <v>9.590676754537563e-12</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_North_America[T.True]</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.02362361430895158</v>
+        <v>0.4698373208221375</v>
       </c>
       <c r="C31" t="n">
-        <v>0.112249509508054</v>
+        <v>0.03332861578287737</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2436286102270238</v>
+        <v>0.4045144342331247</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1963813816091206</v>
+        <v>0.5351602074111503</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8333115702431948</v>
+        <v>3.956166429174619e-45</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2588826584236549</v>
+        <v>0.004135564358761956</v>
       </c>
       <c r="C32" t="n">
-        <v>0.03791786642415234</v>
+        <v>0.00494118969612754</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1845650058617157</v>
+        <v>-0.005548989486428436</v>
       </c>
       <c r="E32" t="n">
-        <v>0.333200310985594</v>
+        <v>0.01382011820395235</v>
       </c>
       <c r="F32" t="n">
-        <v>8.643213406854678e-12</v>
+        <v>0.402616618830528</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004004351756778327</v>
+        <v>0.001079790152347925</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01490079875668908</v>
+        <v>0.00597833807664017</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.03320938066076815</v>
+        <v>-0.01063753716527126</v>
       </c>
       <c r="E33" t="n">
-        <v>0.02520067714721149</v>
+        <v>0.01279711746996711</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7881343596668525</v>
+        <v>0.856668124095525</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4697521047923953</v>
+        <v>-0.01398274283089319</v>
       </c>
       <c r="C34" t="n">
-        <v>0.03481013941747514</v>
+        <v>0.0155897166522796</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4015254852373259</v>
+        <v>-0.04453802599854555</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5379787243474646</v>
+        <v>0.01657254033675916</v>
       </c>
       <c r="F34" t="n">
-        <v>1.680563377038574e-41</v>
+        <v>0.3697611220226221</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001113537143635592</v>
+        <v>0.06813476221211859</v>
       </c>
       <c r="C35" t="n">
-        <v>0.006021031148554734</v>
+        <v>0.07489655592157843</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.01068746705732552</v>
+        <v>-0.07865978996026524</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01291454134459671</v>
+        <v>0.2149293143845024</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8532751009986541</v>
+        <v>0.36297112811455</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,50 +2310,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.004183981957018565</v>
+        <v>0.001915888013808376</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004943082952144705</v>
+        <v>0.004864009007753431</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.005504282601778984</v>
+        <v>-0.007617394461866752</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01387224651581611</v>
+        <v>0.0114491704894835</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3973119774522695</v>
+        <v>0.6936617214919618</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>is_new_manager</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.06842618098902215</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.0763682155861618</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.08125277112344539</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.2181051331014897</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.3702509461405634</v>
-      </c>
-      <c r="G37" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2395,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2427,10 +2375,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-28.63902089506874</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>-2.680600179802938</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4771933030981325</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.938181768271168e-08</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2439,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02313926327038869</v>
+        <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09767080877239748</v>
+        <v>0.1002143663033997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8127260403169279</v>
+        <v>0.79975540801217</v>
       </c>
     </row>
     <row r="4">
@@ -2455,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2234052412627341</v>
+        <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2328794784675677</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3373990767846601</v>
+        <v>0.3364439424069159</v>
       </c>
     </row>
     <row r="5">
@@ -2471,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8180627404127788</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.168995369134968</v>
+        <v>0.1734026513921177</v>
       </c>
       <c r="D5" t="n">
-        <v>1.293561512468184e-06</v>
+        <v>2.563995828054277e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2487,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03544498749501269</v>
+        <v>0.03527526670387295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1931765748363377</v>
+        <v>0.191688294691954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8544175536043231</v>
+        <v>0.853994545471355</v>
       </c>
     </row>
     <row r="7">
@@ -2503,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2759060224168001</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1812662636985352</v>
+        <v>0.1901447102133382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1279831380955545</v>
+        <v>0.1446466431125516</v>
       </c>
     </row>
     <row r="8">
@@ -2519,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1078851505725079</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1932040224873154</v>
+        <v>0.1952515666982443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5765711865505436</v>
+        <v>0.5954095400432464</v>
       </c>
     </row>
     <row r="9">
@@ -2535,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8717785708706234</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1678649184861324</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>2.065612399360983e-07</v>
+        <v>2.539495077342701e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2551,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.03735224036769266</v>
+        <v>-0.04456520772617086</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2698916793365708</v>
+        <v>0.2604021031716313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8899265459788944</v>
+        <v>0.8641137091517834</v>
       </c>
     </row>
     <row r="11">
@@ -2567,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.27139852374157</v>
+        <v>-0.2737623724798149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2816070636601529</v>
+        <v>0.2787881385465057</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3351717854029546</v>
+        <v>0.3261132423877617</v>
       </c>
     </row>
     <row r="12">
@@ -2583,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08472740319915269</v>
+        <v>0.08100487957118127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2580923618181321</v>
+        <v>0.2596429772097166</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7426974963062474</v>
+        <v>0.7550514391424692</v>
       </c>
     </row>
     <row r="13">
@@ -2599,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0406830151843166</v>
+        <v>0.03917827337461736</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2611004769215555</v>
+        <v>0.2572958805743769</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8761799203818157</v>
+        <v>0.8789745077123745</v>
       </c>
     </row>
     <row r="14">
@@ -2615,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0534569388448658</v>
+        <v>-0.05296103812307947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2638638595233255</v>
+        <v>0.2610089865588713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8394532566768507</v>
+        <v>0.8392062624375523</v>
       </c>
     </row>
     <row r="15">
@@ -2631,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1239335042278707</v>
+        <v>0.1181322726534159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2599280592390572</v>
+        <v>0.2572294350577177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.633505078402905</v>
+        <v>0.646055612898408</v>
       </c>
     </row>
     <row r="16">
@@ -2647,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.001862882312047092</v>
+        <v>-0.004000986240379581</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2575901874165238</v>
+        <v>0.2383903410311186</v>
       </c>
       <c r="D16" t="n">
-        <v>0.994229779892155</v>
+        <v>0.9866094604655129</v>
       </c>
     </row>
     <row r="17">
@@ -2663,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1116424378427602</v>
+        <v>0.1057185310395304</v>
       </c>
       <c r="C17" t="n">
-        <v>0.258655496780073</v>
+        <v>0.2543340222421748</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6660132573861222</v>
+        <v>0.6776529122567303</v>
       </c>
     </row>
     <row r="18">
@@ -2679,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1317171712347951</v>
+        <v>-0.1377694895733256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2668604742478565</v>
+        <v>0.2636874203313626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6216023562146854</v>
+        <v>0.6013412201546261</v>
       </c>
     </row>
     <row r="19">
@@ -2695,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02274331928771129</v>
+        <v>-0.02557154094223238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2635260646471042</v>
+        <v>0.252759790153811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.931224861952453</v>
+        <v>0.9194160355966675</v>
       </c>
     </row>
     <row r="20">
@@ -2711,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06665392434454051</v>
+        <v>-0.07344622569376427</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2656595207910754</v>
+        <v>0.267457860954101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8018915682473747</v>
+        <v>0.7836169672222772</v>
       </c>
     </row>
     <row r="21">
@@ -2727,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.209601896539733</v>
+        <v>0.2063167170305059</v>
       </c>
       <c r="C21" t="n">
-        <v>0.248589943238082</v>
+        <v>0.244289653245072</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3991371664160996</v>
+        <v>0.3983578134719846</v>
       </c>
     </row>
     <row r="22">
@@ -2743,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1668969509213569</v>
+        <v>-0.1704634573362026</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2747515022959944</v>
+        <v>0.2696748454965904</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5435543655447144</v>
+        <v>0.5273167196806361</v>
       </c>
     </row>
     <row r="23">
@@ -2759,189 +2711,189 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4971940641809904</v>
+        <v>-0.5008110927334757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2924423487833311</v>
+        <v>0.287067218044571</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0891038687082271</v>
+        <v>0.08105838975171785</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds[T.True]</t>
+          <t>performance_rating_Far_Exceeds[T.True]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26.21442552889307</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+        <v>0.9366864721074267</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1483430409733375</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.713396260923891e-10</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below[T.True]</t>
+          <t>performance_rating_Meets[T.True]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.05451611819325158</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+        <v>-0.5776106069409677</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1143619392421807</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.401383208103943e-07</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds[T.True]</t>
+          <t>region_Europe[T.True]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.15437389964459</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+        <v>0.237316144844174</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1503781926377478</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1145360411757813</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Meets[T.True]</t>
+          <t>region_Latin_America[T.True]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25.63696707854778</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+        <v>-0.04350476117998651</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1611879340386412</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7872365295400213</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Europe[T.True]</t>
+          <t>region_Middle_East_and_Africa[T.True]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2375989005820465</v>
+        <v>-0.07514354096975732</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483942012831661</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1093473930477332</v>
+        <v>0.6414556246120151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Latin_America[T.True]</t>
+          <t>region_North_America[T.True]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.04390400011936763</v>
+        <v>0.09749293462742097</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1581709974633308</v>
+        <v>0.1543265796290165</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7813401518904401</v>
+        <v>0.5275624553510008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa[T.True]</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.07706864556783545</v>
+        <v>-0.002418133412192873</v>
       </c>
       <c r="C30" t="n">
-        <v>0.157805034131052</v>
+        <v>0.007135781003458546</v>
       </c>
       <c r="D30" t="n">
-        <v>0.625281499853628</v>
+        <v>0.7347043603418277</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_North_America[T.True]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.09735884295380272</v>
+        <v>-0.005012017390962195</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1528329758431298</v>
+        <v>0.008304876992455039</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5241067842931748</v>
+        <v>0.5461741835341576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.02140998846971486</v>
+        <v>-0.004129656026475419</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02125751820943617</v>
+        <v>0.02222260881033174</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3138518697695356</v>
+        <v>0.8525770672961279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004963851467076696</v>
+        <v>0.2280638724458785</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008295015527601023</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5495638837808257</v>
+        <v>0.04668969945129923</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.002369150025833512</v>
+        <v>0.006335499136474495</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007250684388762908</v>
+        <v>0.006871422968197181</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7438581373216515</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>is_new_manager</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0.2289921174550882</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.1106079911199388</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.03842392670154298</v>
+        <v>0.3565249957666435</v>
       </c>
     </row>
   </sheetData>
